--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 31,08,26 днрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 31,08,26 днрсч ост зпф.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C12EE74-B38E-4C81-A3BB-29A4D9E44EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE40763-30FD-44D2-A857-191347DFFDF3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -68,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -184,6 +189,12 @@
       </rPr>
       <t xml:space="preserve"> / 46шт в уценку (06,08,26)</t>
     </r>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>07,09,</t>
   </si>
 </sst>
 </file>
@@ -788,46 +799,46 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -865,40 +876,42 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
@@ -965,7 +978,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>287.41000000000003</v>
+        <v>290</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -1008,7 +1021,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="4">
         <f>SUM(AD6:AD500)</f>
-        <v>91.55</v>
+        <v>94</v>
       </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
@@ -1032,10 +1045,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C6" s="1">
         <v>60</v>
@@ -1052,7 +1065,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1104,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="AC6" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AD6" s="1">
-        <f>G6*Q6</f>
+        <f t="shared" ref="AD6:AD14" si="3">G6*Q6</f>
         <v>0</v>
       </c>
       <c r="AE6" s="1"/>
@@ -1132,10 +1145,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C7" s="1">
         <v>9.1340000000000003</v>
@@ -1154,7 +1167,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1170,19 +1183,18 @@
         <v>20</v>
       </c>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:P16" si="3">E7/5</f>
+        <f t="shared" ref="P7:P16" si="4">E7/5</f>
         <v>1.8371999999999999</v>
       </c>
       <c r="Q7" s="5">
-        <f>15*P7-O7-F7</f>
-        <v>7.6099999999999994</v>
+        <v>10</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" ref="R7:R16" si="4">(F7+O7+Q7)/P7</f>
-        <v>15</v>
+        <f t="shared" ref="R7:R16" si="5">(F7+O7+Q7)/P7</f>
+        <v>16.30089266274766</v>
       </c>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S16" si="5">(F7+O7)/P7</f>
+        <f t="shared" ref="S7:S16" si="6">(F7+O7)/P7</f>
         <v>10.857827128238625</v>
       </c>
       <c r="T7" s="1">
@@ -1214,8 +1226,8 @@
       </c>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1">
-        <f>G7*Q7</f>
-        <v>7.6099999999999994</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
@@ -1239,10 +1251,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1">
         <v>109.636</v>
@@ -1259,7 +1271,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1271,18 +1283,18 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S8" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="S8" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T8" s="1">
         <v>0</v>
       </c>
@@ -1311,10 +1323,10 @@
         <v>0.90839999999999999</v>
       </c>
       <c r="AC8" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD8" s="1">
-        <f>G8*Q8</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE8" s="1"/>
@@ -1339,10 +1351,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1">
         <v>130</v>
@@ -1359,7 +1371,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1371,18 +1383,18 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="S9" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T9" s="1">
         <v>1.8</v>
       </c>
@@ -1411,10 +1423,10 @@
         <v>2.4</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD9" s="1">
-        <f>G9*Q9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE9" s="1"/>
@@ -1439,10 +1451,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -1463,7 +1475,7 @@
         <v>120</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1477,19 +1489,18 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.4</v>
       </c>
       <c r="Q10" s="5">
-        <f>12*P10-O10-F10</f>
-        <v>111.80000000000001</v>
+        <v>110</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="4"/>
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>11.826923076923077</v>
       </c>
       <c r="S10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.25</v>
       </c>
       <c r="T10" s="1">
@@ -1521,8 +1532,8 @@
       </c>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1">
-        <f>G10*Q10</f>
-        <v>33.54</v>
+        <f t="shared" si="3"/>
+        <v>33</v>
       </c>
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
@@ -1546,10 +1557,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1">
         <v>172</v>
@@ -1570,7 +1581,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1584,19 +1595,18 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>18.8</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" ref="Q10:Q11" si="6">15*P11-O11-F11</f>
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R11" s="1">
-        <f t="shared" si="4"/>
-        <v>15</v>
+        <f t="shared" si="5"/>
+        <v>15.106382978723405</v>
       </c>
       <c r="S11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.0638297872340425</v>
       </c>
       <c r="T11" s="1">
@@ -1628,8 +1638,8 @@
       </c>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1">
-        <f>G11*Q11</f>
-        <v>50.4</v>
+        <f t="shared" si="3"/>
+        <v>51</v>
       </c>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
@@ -1653,10 +1663,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>42</v>
@@ -1677,7 +1687,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1693,18 +1703,18 @@
         <v>50</v>
       </c>
       <c r="P12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="1">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="S12" s="1">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
+      <c r="S12" s="1">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
       <c r="T12" s="1">
         <v>9.4</v>
       </c>
@@ -1734,7 +1744,7 @@
       </c>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1">
-        <f>G12*Q12</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE12" s="1"/>
@@ -1759,10 +1769,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
@@ -1783,7 +1793,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1797,18 +1807,18 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="1">
-        <f t="shared" si="4"/>
-        <v>34.565217391304351</v>
-      </c>
-      <c r="S13" s="1">
         <f t="shared" si="5"/>
         <v>34.565217391304351</v>
       </c>
+      <c r="S13" s="1">
+        <f t="shared" si="6"/>
+        <v>34.565217391304351</v>
+      </c>
       <c r="T13" s="1">
         <v>9.1999999999999993</v>
       </c>
@@ -1838,7 +1848,7 @@
       </c>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1">
-        <f>G13*Q13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE13" s="1"/>
@@ -1863,10 +1873,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
@@ -1885,7 +1895,7 @@
         <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1901,18 +1911,18 @@
         <v>60</v>
       </c>
       <c r="P14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="1">
-        <f t="shared" si="4"/>
-        <v>26.03448275862069</v>
-      </c>
-      <c r="S14" s="1">
         <f t="shared" si="5"/>
         <v>26.03448275862069</v>
       </c>
+      <c r="S14" s="1">
+        <f t="shared" si="6"/>
+        <v>26.03448275862069</v>
+      </c>
       <c r="T14" s="1">
         <v>11.8</v>
       </c>
@@ -1942,7 +1952,7 @@
       </c>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1">
-        <f>G14*Q14</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE14" s="1"/>
@@ -1967,10 +1977,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="9">
         <v>84</v>
@@ -1985,7 +1995,7 @@
         <v>120</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
@@ -1997,18 +2007,18 @@
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
       <c r="P15" s="9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q15" s="11"/>
       <c r="R15" s="9" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S15" s="9" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="S15" s="9" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T15" s="9">
         <v>0.4</v>
       </c>
@@ -2037,7 +2047,7 @@
         <v>1.6</v>
       </c>
       <c r="AC15" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AD15" s="9"/>
       <c r="AE15" s="1"/>
@@ -2062,10 +2072,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1">
         <v>284</v>
@@ -2084,7 +2094,7 @@
         <v>180</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2098,18 +2108,18 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1">
-        <f t="shared" si="4"/>
-        <v>35.571428571428569</v>
-      </c>
-      <c r="S16" s="1">
         <f t="shared" si="5"/>
         <v>35.571428571428569</v>
       </c>
+      <c r="S16" s="1">
+        <f t="shared" si="6"/>
+        <v>35.571428571428569</v>
+      </c>
       <c r="T16" s="1">
         <v>4.4000000000000004</v>
       </c>
@@ -2138,7 +2148,7 @@
         <v>6.2</v>
       </c>
       <c r="AC16" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AD16" s="1">
         <f>G16*Q16</f>
